--- a/Links PLP Scrapping.xlsx
+++ b/Links PLP Scrapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ncrespo\Desktop\Nike_Scrapper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ncrespo\Desktop\Nike_Scrapper_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418317C5-EA59-4188-8247-EF57AEB3E86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2F845C-8837-4BF6-A84A-B69177E680A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Running" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="191">
   <si>
     <t>Franquicia</t>
   </si>
@@ -1743,6 +1743,24 @@
   </si>
   <si>
     <t>Winflo/</t>
+  </si>
+  <si>
+    <t>Air Jordan 1 Kids</t>
+  </si>
+  <si>
+    <t>Dunk Low Kids</t>
+  </si>
+  <si>
+    <t>Air Force 1 Kids</t>
+  </si>
+  <si>
+    <t>Stellar Ride Kids</t>
+  </si>
+  <si>
+    <t>Flex Runner Kids</t>
+  </si>
+  <si>
+    <t>Cosmic Runner Kids</t>
   </si>
 </sst>
 </file>
@@ -2052,7 +2070,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
@@ -2320,6 +2338,21 @@
       </c>
       <c r="C24" s="3" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2380,7 +2413,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2508,28 +2541,46 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
+      <c r="A13" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="3"/>
+      <c r="A14" s="5" t="s">
+        <v>187</v>
+      </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="3"/>
+      <c r="A15" s="5"/>
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
+      <c r="A16" s="5"/>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="3"/>
+      <c r="A17" s="5"/>
       <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A21" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
